--- a/etf_holdings/2026-09-30_common_daily_changes_summary.xlsx
+++ b/etf_holdings/2026-09-30_common_daily_changes_summary.xlsx
@@ -490,11 +490,11 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>全部加碼</t>
+          <t>混合</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -504,49 +504,49 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>00990A(全數賣出)</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>1303</t>
+          <t>6223</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>南亞</t>
+          <t>旺矽</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>全部加碼</t>
+          <t>全部減碼</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>00991A(1,000,000)、00400A(540,000)</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>00991A(-149,000)、00403A(-100,000)、00990A(全數賣出)</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>6223</t>
+          <t>1303</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>旺矽</t>
+          <t>南亞</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -554,17 +554,17 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>全部減碼</t>
+          <t>全部加碼</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
+          <t>00991A(1,000,000)、00400A(540,000)</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
           <t>-</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>00991A(-149,000)、00403A(-100,000)</t>
         </is>
       </c>
     </row>
